--- a/constructii.xlsx
+++ b/constructii.xlsx
@@ -874,12 +874,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VIZUALIZAREA REZULTATELOR</t>
+          <t>VIZUALIZAREA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VIZUALIZAREA REZULTATELOR</t>
+          <t>VIZUALIZAREA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DASHBOARD</t>
+          <t>COMPOZIȚIE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>COMPUNEREA DASHBOARD-ULUI</t>
+          <t>COMPUNEREA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>COMPUNEREA DASHBOARD-ULUI EXECUTIV</t>
+          <t>COMPUNEREA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>MESAJ</t>
+          <t>SINTEZĂ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SINTETIZAREA MESAJULUI</t>
+          <t>SINTETIZAREA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SINTETIZAREA MESAJULUI DIN DATE</t>
+          <t>SINTETIZAREA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -965,17 +965,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DECIZIE</t>
+          <t>LIVRARE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LIVRAREA RAPORTULUI</t>
+          <t>LIVRAREA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LIVRAREA RAPORTULUI DE DECIZIE</t>
+          <t>LIVRAREA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -997,22 +997,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CLOUD</t>
+          <t>SISTEM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DISTRIBUIREA ÎN CLOUD</t>
+          <t>SISTEMATIZAREA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DISTRIBUIREA ÎN CLOUD</t>
+          <t>SISTEMATIZAREA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DISTRIBUI</t>
+          <t>SISTEMATIZEZ</t>
         </is>
       </c>
     </row>
@@ -1029,22 +1029,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SINCRONIZARE</t>
+          <t>MOTOR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SINCRONIZAREA CU DATELE</t>
+          <t>AUTOMATIZAREA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SINCRONIZAREA CU DATELE</t>
+          <t>AUTOMATIZAREA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SINCRONIZEZ</t>
+          <t>AUTOMATIZEZ</t>
         </is>
       </c>
     </row>
@@ -1066,17 +1066,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MONITORIZAREA SERVICIULUI</t>
+          <t>GUVERNAREA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MONITORIZAREA SERVICIULUI</t>
+          <t>GUVERNAREA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MONITORIZEZ</t>
+          <t>GUVERNEZ</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DELEGAREA CĂTRE SISTEM</t>
+          <t>DELEGAREA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>DELEGAREA CĂTRE SISTEMUL AUTONOM</t>
+          <t>DELEGAREA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
